--- a/output/StructureDefinition-pdex-provider-member-no-match.xlsx
+++ b/output/StructureDefinition-pdex-provider-member-no-match.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T22:49:33-04:00</t>
+    <t>2026-03-19T09:51:30-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-pdex-provider-member-no-match.xlsx
+++ b/output/StructureDefinition-pdex-provider-member-no-match.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:51:30-04:00</t>
+    <t>2026-03-31T21:00:10-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-pdex-provider-member-no-match.xlsx
+++ b/output/StructureDefinition-pdex-provider-member-no-match.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T21:00:10-04:00</t>
+    <t>2026-05-29T12:37:47-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -639,14 +639,14 @@
     <t>Group.managingEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
     <t>Payer managing this group</t>
   </si>
   <si>
-    <t>Reference to the payer organization that performed the member match</t>
+    <t>Reference to the payer organization that performed the member match. Constrained to Organization since the managing entity is always a Payer (i.e., a healthcare organization), not a Practitioner, PractitionerRole, or RelatedPerson.</t>
   </si>
   <si>
     <t>This does not strictly align with ownership of a herd or flock, but may suffice to represent that relationship in simple cases. More complex cases will require an extension.</t>
